--- a/S15/T174/S15_T174_decision_1.xlsx
+++ b/S15/T174/S15_T174_decision_1.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="72">
   <si>
     <t xml:space="preserve">c1</t>
   </si>
@@ -139,63 +139,69 @@
     <t xml:space="preserve">x 1 batch</t>
   </si>
   <si>
+    <t xml:space="preserve">Milan</t>
+  </si>
+  <si>
     <t xml:space="preserve">Puree Purchasing</t>
   </si>
   <si>
     <t xml:space="preserve">x 1 bin</t>
   </si>
   <si>
+    <t xml:space="preserve">Rome</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Concentrate Purchasing for Arnhem</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Madrid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Warsaw</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cordial packaging</t>
+  </si>
+  <si>
+    <t xml:space="preserve">x 20 pallets</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rauma</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cordial production</t>
+  </si>
+  <si>
     <t xml:space="preserve">Kemijarvi</t>
   </si>
   <si>
-    <t xml:space="preserve">Concentrate Purchasing for Arnhem</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rauma</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cordial packaging</t>
-  </si>
-  <si>
-    <t xml:space="preserve">x 20 pallets</t>
-  </si>
-  <si>
     <t xml:space="preserve">Berlin</t>
   </si>
   <si>
-    <t xml:space="preserve">Cordial production</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Madrid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Milan</t>
-  </si>
-  <si>
     <t xml:space="preserve">Bottle Purchasing</t>
   </si>
   <si>
+    <t xml:space="preserve">Sugar Purchasing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">x 1 tonne</t>
+  </si>
+  <si>
     <t xml:space="preserve">Budapest</t>
   </si>
   <si>
-    <t xml:space="preserve">Sugar Purchasing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">x 1 tonne</t>
-  </si>
-  <si>
     <t xml:space="preserve">Concentrate Purchasing for Vesoul</t>
   </si>
   <si>
+    <t xml:space="preserve">Bucharest</t>
+  </si>
+  <si>
     <t xml:space="preserve">CCFFCC</t>
   </si>
   <si>
     <t xml:space="preserve">Intercontinental transport</t>
   </si>
   <si>
-    <t xml:space="preserve">Warsaw</t>
-  </si>
-  <si>
     <t xml:space="preserve">Puree transport to Arnhem</t>
   </si>
   <si>
@@ -206,9 +212,6 @@
   </si>
   <si>
     <t xml:space="preserve">FFFF99</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bucharest</t>
   </si>
   <si>
     <t xml:space="preserve">Production in New-Zeland</t>
@@ -1574,7 +1577,9 @@
       <c r="C11" s="22" t="s">
         <v>22</v>
       </c>
-      <c r="D11" s="23"/>
+      <c r="D11" s="23" t="n">
+        <v>65</v>
+      </c>
       <c r="E11" s="24"/>
       <c r="F11" s="24"/>
       <c r="G11" s="25"/>
@@ -1589,7 +1594,7 @@
         <v>26</v>
       </c>
       <c r="K11" s="28" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="L11" s="29" t="s">
         <v>27</v>
@@ -1606,7 +1611,9 @@
         <v>29</v>
       </c>
       <c r="D12" s="30"/>
-      <c r="E12" s="31"/>
+      <c r="E12" s="31" t="n">
+        <v>44</v>
+      </c>
       <c r="F12" s="31"/>
       <c r="G12" s="32"/>
       <c r="H12" s="26" t="str">
@@ -1620,7 +1627,7 @@
         <v>30</v>
       </c>
       <c r="K12" s="34" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L12" s="35" t="s">
         <v>31</v>
@@ -1688,13 +1695,13 @@
         <v>25</v>
       </c>
       <c r="C15" s="41" t="s">
-        <v>22</v>
-      </c>
-      <c r="D15" s="31" t="n">
-        <v>29</v>
-      </c>
+        <v>33</v>
+      </c>
+      <c r="D15" s="31"/>
       <c r="E15" s="31"/>
-      <c r="F15" s="31"/>
+      <c r="F15" s="31" t="n">
+        <v>12</v>
+      </c>
       <c r="G15" s="32"/>
       <c r="H15" s="26" t="str">
         <f aca="false">IF(AND(B15="",OR(C15&lt;&gt;"",D15&lt;&gt;"",E15&lt;&gt;"",F15&lt;&gt;"",G15&lt;&gt;"")),"A lorry must be selected",IF(AND(C15="",OR(D15&lt;&gt;"",E15&lt;&gt;"",F15&lt;&gt;"",G15&lt;&gt;"")),"A town must be selected",""))</f>
@@ -1706,9 +1713,7 @@
       <c r="J15" s="33" t="s">
         <v>37</v>
       </c>
-      <c r="K15" s="34" t="n">
-        <v>8</v>
-      </c>
+      <c r="K15" s="34"/>
       <c r="L15" s="35" t="s">
         <v>38</v>
       </c>
@@ -1721,13 +1726,13 @@
         <v>25</v>
       </c>
       <c r="C16" s="41" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="D16" s="31"/>
-      <c r="E16" s="31" t="n">
-        <v>29</v>
-      </c>
-      <c r="F16" s="31"/>
+      <c r="E16" s="31"/>
+      <c r="F16" s="31" t="n">
+        <v>17</v>
+      </c>
       <c r="G16" s="32"/>
       <c r="H16" s="26" t="str">
         <f aca="false">IF(AND(B16="",OR(C16&lt;&gt;"",D16&lt;&gt;"",E16&lt;&gt;"",F16&lt;&gt;"",G16&lt;&gt;"")),"A lorry must be selected",IF(AND(C16="",OR(D16&lt;&gt;"",E16&lt;&gt;"",F16&lt;&gt;"",G16&lt;&gt;"")),"A town must be selected",""))</f>
@@ -1737,13 +1742,13 @@
         <v>6</v>
       </c>
       <c r="J16" s="33" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K16" s="34" t="n">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="L16" s="35" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1754,16 +1759,14 @@
         <v>25</v>
       </c>
       <c r="C17" s="41" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D17" s="31"/>
       <c r="E17" s="31"/>
       <c r="F17" s="31" t="n">
-        <v>13</v>
-      </c>
-      <c r="G17" s="32" t="n">
-        <v>13</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="G17" s="32"/>
       <c r="H17" s="26" t="str">
         <f aca="false">IF(AND(B17="",OR(C17&lt;&gt;"",D17&lt;&gt;"",E17&lt;&gt;"",F17&lt;&gt;"",G17&lt;&gt;"")),"A lorry must be selected",IF(AND(C17="",OR(D17&lt;&gt;"",E17&lt;&gt;"",F17&lt;&gt;"",G17&lt;&gt;"")),"A town must be selected",""))</f>
         <v/>
@@ -1772,11 +1775,13 @@
         <v>7</v>
       </c>
       <c r="J17" s="42" t="s">
-        <v>42</v>
-      </c>
-      <c r="K17" s="43"/>
+        <v>43</v>
+      </c>
+      <c r="K17" s="43" t="n">
+        <v>8</v>
+      </c>
       <c r="L17" s="44" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1787,16 +1792,14 @@
         <v>25</v>
       </c>
       <c r="C18" s="41" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D18" s="31"/>
       <c r="E18" s="31"/>
       <c r="F18" s="31" t="n">
         <v>16</v>
       </c>
-      <c r="G18" s="32" t="n">
-        <v>16</v>
-      </c>
+      <c r="G18" s="32"/>
       <c r="H18" s="26" t="str">
         <f aca="false">IF(AND(B18="",OR(C18&lt;&gt;"",D18&lt;&gt;"",E18&lt;&gt;"",F18&lt;&gt;"",G18&lt;&gt;"")),"A lorry must be selected",IF(AND(C18="",OR(D18&lt;&gt;"",E18&lt;&gt;"",F18&lt;&gt;"",G18&lt;&gt;"")),"A town must be selected",""))</f>
         <v/>
@@ -1813,7 +1816,7 @@
         <v>22</v>
       </c>
       <c r="D19" s="31" t="n">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="E19" s="31"/>
       <c r="F19" s="31"/>
@@ -1831,15 +1834,15 @@
         <v>10</v>
       </c>
       <c r="B20" s="40" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="C20" s="41" t="s">
-        <v>29</v>
-      </c>
-      <c r="D20" s="31"/>
-      <c r="E20" s="31" t="n">
-        <v>29</v>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="D20" s="31" t="n">
+        <v>24</v>
+      </c>
+      <c r="E20" s="31"/>
       <c r="F20" s="31"/>
       <c r="G20" s="32"/>
       <c r="H20" s="26" t="str">
@@ -1852,19 +1855,17 @@
         <v>11</v>
       </c>
       <c r="B21" s="40" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="C21" s="41" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="D21" s="31"/>
       <c r="E21" s="31"/>
       <c r="F21" s="31" t="n">
-        <v>13</v>
-      </c>
-      <c r="G21" s="32" t="n">
-        <v>13</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="G21" s="32"/>
       <c r="H21" s="26" t="str">
         <f aca="false">IF(AND(B21="",OR(C21&lt;&gt;"",D21&lt;&gt;"",E21&lt;&gt;"",F21&lt;&gt;"",G21&lt;&gt;"")),"A lorry must be selected",IF(AND(C21="",OR(D21&lt;&gt;"",E21&lt;&gt;"",F21&lt;&gt;"",G21&lt;&gt;"")),"A town must be selected",""))</f>
         <v/>
@@ -1873,13 +1874,13 @@
         <v>1</v>
       </c>
       <c r="J21" s="45" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="K21" s="28" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="L21" s="45" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1887,19 +1888,17 @@
         <v>12</v>
       </c>
       <c r="B22" s="40" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="C22" s="41" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D22" s="31"/>
       <c r="E22" s="31"/>
       <c r="F22" s="31" t="n">
-        <v>16</v>
-      </c>
-      <c r="G22" s="32" t="n">
-        <v>16</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="G22" s="32"/>
       <c r="H22" s="26" t="str">
         <f aca="false">IF(AND(B22="",OR(C22&lt;&gt;"",D22&lt;&gt;"",E22&lt;&gt;"",F22&lt;&gt;"",G22&lt;&gt;"")),"A lorry must be selected",IF(AND(C22="",OR(D22&lt;&gt;"",E22&lt;&gt;"",F22&lt;&gt;"",G22&lt;&gt;"")),"A town must be selected",""))</f>
         <v/>
@@ -1908,10 +1907,10 @@
         <v>2</v>
       </c>
       <c r="J22" s="46" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="K22" s="34" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L22" s="46" t="s">
         <v>31</v>
@@ -1922,16 +1921,16 @@
         <v>13</v>
       </c>
       <c r="B23" s="40" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="C23" s="41" t="s">
-        <v>22</v>
-      </c>
-      <c r="D23" s="31" t="n">
-        <v>66</v>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="D23" s="31"/>
       <c r="E23" s="31"/>
-      <c r="F23" s="31"/>
+      <c r="F23" s="31" t="n">
+        <v>4</v>
+      </c>
       <c r="G23" s="32"/>
       <c r="H23" s="26" t="str">
         <f aca="false">IF(AND(B23="",OR(C23&lt;&gt;"",D23&lt;&gt;"",E23&lt;&gt;"",F23&lt;&gt;"",G23&lt;&gt;"")),"A lorry must be selected",IF(AND(C23="",OR(D23&lt;&gt;"",E23&lt;&gt;"",F23&lt;&gt;"",G23&lt;&gt;"")),"A town must be selected",""))</f>
@@ -1965,16 +1964,14 @@
         <v>14</v>
       </c>
       <c r="B24" s="40" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="C24" s="41" t="s">
-        <v>48</v>
+        <v>22</v>
       </c>
       <c r="D24" s="31"/>
       <c r="E24" s="31"/>
-      <c r="F24" s="31" t="n">
-        <v>18</v>
-      </c>
+      <c r="F24" s="31"/>
       <c r="G24" s="32"/>
       <c r="H24" s="26" t="str">
         <f aca="false">IF(AND(B24="",OR(C24&lt;&gt;"",D24&lt;&gt;"",E24&lt;&gt;"",F24&lt;&gt;"",G24&lt;&gt;"")),"A lorry must be selected",IF(AND(C24="",OR(D24&lt;&gt;"",E24&lt;&gt;"",F24&lt;&gt;"",G24&lt;&gt;"")),"A town must be selected",""))</f>
@@ -1999,12 +1996,12 @@
         <v>25</v>
       </c>
       <c r="C25" s="41" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D25" s="31"/>
       <c r="E25" s="31"/>
       <c r="F25" s="31" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="G25" s="32"/>
       <c r="H25" s="26" t="str">
@@ -2015,10 +2012,10 @@
         <v>5</v>
       </c>
       <c r="J25" s="46" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="K25" s="34" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="L25" s="46" t="s">
         <v>38</v>
@@ -2032,13 +2029,13 @@
         <v>25</v>
       </c>
       <c r="C26" s="41" t="s">
-        <v>51</v>
+        <v>29</v>
       </c>
       <c r="D26" s="31"/>
-      <c r="E26" s="31"/>
-      <c r="F26" s="31" t="n">
-        <v>27</v>
-      </c>
+      <c r="E26" s="31" t="n">
+        <v>21</v>
+      </c>
+      <c r="F26" s="31"/>
       <c r="G26" s="32"/>
       <c r="H26" s="26" t="str">
         <f aca="false">IF(AND(B26="",OR(C26&lt;&gt;"",D26&lt;&gt;"",E26&lt;&gt;"",F26&lt;&gt;"",G26&lt;&gt;"")),"A lorry must be selected",IF(AND(C26="",OR(D26&lt;&gt;"",E26&lt;&gt;"",F26&lt;&gt;"",G26&lt;&gt;"")),"A town must be selected",""))</f>
@@ -2048,13 +2045,13 @@
         <v>6</v>
       </c>
       <c r="J26" s="46" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K26" s="34" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="L26" s="46" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2065,14 +2062,16 @@
         <v>25</v>
       </c>
       <c r="C27" s="41" t="s">
-        <v>22</v>
-      </c>
-      <c r="D27" s="31" t="n">
-        <v>29</v>
-      </c>
+        <v>55</v>
+      </c>
+      <c r="D27" s="31"/>
       <c r="E27" s="31"/>
-      <c r="F27" s="31"/>
-      <c r="G27" s="32"/>
+      <c r="F27" s="31" t="n">
+        <v>14</v>
+      </c>
+      <c r="G27" s="32" t="n">
+        <v>9</v>
+      </c>
       <c r="H27" s="26" t="str">
         <f aca="false">IF(AND(B27="",OR(C27&lt;&gt;"",D27&lt;&gt;"",E27&lt;&gt;"",F27&lt;&gt;"",G27&lt;&gt;"")),"A lorry must be selected",IF(AND(C27="",OR(D27&lt;&gt;"",E27&lt;&gt;"",F27&lt;&gt;"",G27&lt;&gt;"")),"A town must be selected",""))</f>
         <v/>
@@ -2081,11 +2080,11 @@
         <v>7</v>
       </c>
       <c r="J27" s="47" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="K27" s="43"/>
       <c r="L27" s="47" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2096,20 +2095,22 @@
         <v>25</v>
       </c>
       <c r="C28" s="41" t="s">
-        <v>29</v>
+        <v>57</v>
       </c>
       <c r="D28" s="31"/>
-      <c r="E28" s="31" t="n">
-        <v>29</v>
-      </c>
-      <c r="F28" s="31"/>
-      <c r="G28" s="32"/>
+      <c r="E28" s="31"/>
+      <c r="F28" s="31" t="n">
+        <v>11</v>
+      </c>
+      <c r="G28" s="32" t="n">
+        <v>4</v>
+      </c>
       <c r="H28" s="26" t="str">
         <f aca="false">IF(AND(B28="",OR(C28&lt;&gt;"",D28&lt;&gt;"",E28&lt;&gt;"",F28&lt;&gt;"",G28&lt;&gt;"")),"A lorry must be selected",IF(AND(C28="",OR(D28&lt;&gt;"",E28&lt;&gt;"",F28&lt;&gt;"",G28&lt;&gt;"")),"A town must be selected",""))</f>
         <v/>
       </c>
       <c r="J28" s="1" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2120,13 +2121,13 @@
         <v>25</v>
       </c>
       <c r="C29" s="41" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="D29" s="31"/>
       <c r="E29" s="31"/>
       <c r="F29" s="31"/>
       <c r="G29" s="32" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="H29" s="26" t="str">
         <f aca="false">IF(AND(B29="",OR(C29&lt;&gt;"",D29&lt;&gt;"",E29&lt;&gt;"",F29&lt;&gt;"",G29&lt;&gt;"")),"A lorry must be selected",IF(AND(C29="",OR(D29&lt;&gt;"",E29&lt;&gt;"",F29&lt;&gt;"",G29&lt;&gt;"")),"A town must be selected",""))</f>
@@ -2141,20 +2142,20 @@
         <v>25</v>
       </c>
       <c r="C30" s="41" t="s">
-        <v>51</v>
+        <v>29</v>
       </c>
       <c r="D30" s="31"/>
-      <c r="E30" s="31"/>
+      <c r="E30" s="31" t="n">
+        <v>8</v>
+      </c>
       <c r="F30" s="31"/>
-      <c r="G30" s="32" t="n">
-        <v>16</v>
-      </c>
+      <c r="G30" s="32"/>
       <c r="H30" s="26" t="str">
         <f aca="false">IF(AND(B30="",OR(C30&lt;&gt;"",D30&lt;&gt;"",E30&lt;&gt;"",F30&lt;&gt;"",G30&lt;&gt;"")),"A lorry must be selected",IF(AND(C30="",OR(D30&lt;&gt;"",E30&lt;&gt;"",F30&lt;&gt;"",G30&lt;&gt;"")),"A town must be selected",""))</f>
         <v/>
       </c>
       <c r="J30" s="48" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="K30" s="48"/>
       <c r="L30" s="48"/>
@@ -2167,14 +2168,14 @@
         <v>25</v>
       </c>
       <c r="C31" s="41" t="s">
-        <v>57</v>
+        <v>33</v>
       </c>
       <c r="D31" s="31"/>
       <c r="E31" s="31"/>
-      <c r="F31" s="31" t="n">
-        <v>29</v>
-      </c>
-      <c r="G31" s="32"/>
+      <c r="F31" s="31"/>
+      <c r="G31" s="32" t="n">
+        <v>8</v>
+      </c>
       <c r="H31" s="26" t="str">
         <f aca="false">IF(AND(B31="",OR(C31&lt;&gt;"",D31&lt;&gt;"",E31&lt;&gt;"",F31&lt;&gt;"",G31&lt;&gt;"")),"A lorry must be selected",IF(AND(C31="",OR(D31&lt;&gt;"",E31&lt;&gt;"",F31&lt;&gt;"",G31&lt;&gt;"")),"A town must be selected",""))</f>
         <v/>
@@ -2184,12 +2185,18 @@
       <c r="A32" s="1" t="n">
         <v>22</v>
       </c>
-      <c r="B32" s="40"/>
-      <c r="C32" s="41"/>
+      <c r="B32" s="40" t="s">
+        <v>28</v>
+      </c>
+      <c r="C32" s="41" t="s">
+        <v>39</v>
+      </c>
       <c r="D32" s="31"/>
       <c r="E32" s="31"/>
       <c r="F32" s="31"/>
-      <c r="G32" s="32"/>
+      <c r="G32" s="32" t="n">
+        <v>10</v>
+      </c>
       <c r="H32" s="26" t="str">
         <f aca="false">IF(AND(B32="",OR(C32&lt;&gt;"",D32&lt;&gt;"",E32&lt;&gt;"",F32&lt;&gt;"",G32&lt;&gt;"")),"A lorry must be selected",IF(AND(C32="",OR(D32&lt;&gt;"",E32&lt;&gt;"",F32&lt;&gt;"",G32&lt;&gt;"")),"A town must be selected",""))</f>
         <v/>
@@ -2198,25 +2205,31 @@
         <v>1</v>
       </c>
       <c r="J32" s="49" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="K32" s="28" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="L32" s="49" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="1" t="n">
         <v>23</v>
       </c>
-      <c r="B33" s="40"/>
-      <c r="C33" s="41"/>
+      <c r="B33" s="40" t="s">
+        <v>28</v>
+      </c>
+      <c r="C33" s="41" t="s">
+        <v>42</v>
+      </c>
       <c r="D33" s="31"/>
       <c r="E33" s="31"/>
       <c r="F33" s="31"/>
-      <c r="G33" s="32"/>
+      <c r="G33" s="32" t="n">
+        <v>8</v>
+      </c>
       <c r="H33" s="26" t="str">
         <f aca="false">IF(AND(B33="",OR(C33&lt;&gt;"",D33&lt;&gt;"",E33&lt;&gt;"",F33&lt;&gt;"",G33&lt;&gt;"")),"A lorry must be selected",IF(AND(C33="",OR(D33&lt;&gt;"",E33&lt;&gt;"",F33&lt;&gt;"",G33&lt;&gt;"")),"A town must be selected",""))</f>
         <v/>
@@ -2225,13 +2238,13 @@
         <v>2</v>
       </c>
       <c r="J33" s="50" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="K33" s="34" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L33" s="50" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2242,14 +2255,14 @@
         <v>28</v>
       </c>
       <c r="C34" s="41" t="s">
-        <v>22</v>
-      </c>
-      <c r="D34" s="31" t="n">
-        <v>29</v>
-      </c>
+        <v>44</v>
+      </c>
+      <c r="D34" s="31"/>
       <c r="E34" s="31"/>
       <c r="F34" s="31"/>
-      <c r="G34" s="32"/>
+      <c r="G34" s="32" t="n">
+        <v>5</v>
+      </c>
       <c r="H34" s="26" t="str">
         <f aca="false">IF(AND(B34="",OR(C34&lt;&gt;"",D34&lt;&gt;"",E34&lt;&gt;"",F34&lt;&gt;"",G34&lt;&gt;"")),"A lorry must be selected",IF(AND(C34="",OR(D34&lt;&gt;"",E34&lt;&gt;"",F34&lt;&gt;"",G34&lt;&gt;"")),"A town must be selected",""))</f>
         <v/>
@@ -2258,13 +2271,13 @@
         <v>3</v>
       </c>
       <c r="J34" s="51" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="K34" s="43" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="L34" s="51" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2275,20 +2288,20 @@
         <v>28</v>
       </c>
       <c r="C35" s="41" t="s">
-        <v>29</v>
+        <v>51</v>
       </c>
       <c r="D35" s="31"/>
-      <c r="E35" s="31" t="n">
-        <v>29</v>
-      </c>
+      <c r="E35" s="31"/>
       <c r="F35" s="31"/>
-      <c r="G35" s="32"/>
+      <c r="G35" s="32" t="n">
+        <v>7</v>
+      </c>
       <c r="H35" s="26" t="str">
         <f aca="false">IF(AND(B35="",OR(C35&lt;&gt;"",D35&lt;&gt;"",E35&lt;&gt;"",F35&lt;&gt;"",G35&lt;&gt;"")),"A lorry must be selected",IF(AND(C35="",OR(D35&lt;&gt;"",E35&lt;&gt;"",F35&lt;&gt;"",G35&lt;&gt;"")),"A town must be selected",""))</f>
         <v/>
       </c>
       <c r="J35" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2299,15 +2312,13 @@
         <v>28</v>
       </c>
       <c r="C36" s="41" t="s">
-        <v>62</v>
+        <v>48</v>
       </c>
       <c r="D36" s="31"/>
       <c r="E36" s="31"/>
-      <c r="F36" s="31" t="n">
-        <v>29</v>
-      </c>
+      <c r="F36" s="31"/>
       <c r="G36" s="32" t="n">
-        <v>29</v>
+        <v>7</v>
       </c>
       <c r="H36" s="26" t="str">
         <f aca="false">IF(AND(B36="",OR(C36&lt;&gt;"",D36&lt;&gt;"",E36&lt;&gt;"",F36&lt;&gt;"",G36&lt;&gt;"")),"A lorry must be selected",IF(AND(C36="",OR(D36&lt;&gt;"",E36&lt;&gt;"",F36&lt;&gt;"",G36&lt;&gt;"")),"A town must be selected",""))</f>
@@ -2329,7 +2340,7 @@
         <v/>
       </c>
       <c r="J37" s="52" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="K37" s="52"/>
       <c r="L37" s="52"/>
@@ -2338,12 +2349,18 @@
       <c r="A38" s="1" t="n">
         <v>28</v>
       </c>
-      <c r="B38" s="40"/>
-      <c r="C38" s="41"/>
+      <c r="B38" s="40" t="s">
+        <v>28</v>
+      </c>
+      <c r="C38" s="41" t="s">
+        <v>50</v>
+      </c>
       <c r="D38" s="31"/>
       <c r="E38" s="31"/>
       <c r="F38" s="31"/>
-      <c r="G38" s="32"/>
+      <c r="G38" s="32" t="n">
+        <v>7</v>
+      </c>
       <c r="H38" s="26" t="str">
         <f aca="false">IF(AND(B38="",OR(C38&lt;&gt;"",D38&lt;&gt;"",E38&lt;&gt;"",F38&lt;&gt;"",G38&lt;&gt;"")),"A lorry must be selected",IF(AND(C38="",OR(D38&lt;&gt;"",E38&lt;&gt;"",F38&lt;&gt;"",G38&lt;&gt;"")),"A town must be selected",""))</f>
         <v/>
@@ -2353,8 +2370,12 @@
       <c r="A39" s="1" t="n">
         <v>29</v>
       </c>
-      <c r="B39" s="40"/>
-      <c r="C39" s="41"/>
+      <c r="B39" s="40" t="s">
+        <v>28</v>
+      </c>
+      <c r="C39" s="41" t="s">
+        <v>29</v>
+      </c>
       <c r="D39" s="31"/>
       <c r="E39" s="31"/>
       <c r="F39" s="31"/>
@@ -2364,7 +2385,7 @@
         <v/>
       </c>
       <c r="J39" s="53" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2400,13 +2421,13 @@
         <v>1</v>
       </c>
       <c r="J41" s="55" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="K41" s="28" t="n">
         <v>15</v>
       </c>
       <c r="L41" s="55" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="M41" s="56"/>
     </row>
@@ -2430,7 +2451,9 @@
       <c r="J42" s="57" t="s">
         <v>34</v>
       </c>
-      <c r="K42" s="34"/>
+      <c r="K42" s="34" t="n">
+        <v>2</v>
+      </c>
       <c r="L42" s="57" t="s">
         <v>35</v>
       </c>
@@ -2478,11 +2501,11 @@
         <v>4</v>
       </c>
       <c r="J44" s="57" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="K44" s="34"/>
       <c r="L44" s="57" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2503,11 +2526,11 @@
         <v>5</v>
       </c>
       <c r="J45" s="58" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="K45" s="43"/>
       <c r="L45" s="58" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2525,7 +2548,7 @@
         <v/>
       </c>
       <c r="J46" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2902,7 +2925,7 @@
     </row>
     <row r="71" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B71" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
   </sheetData>
